--- a/tests/fixtures/wide/genuine-oak-wide-species.xlsx
+++ b/tests/fixtures/wide/genuine-oak-wide-species.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pricelist" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Options" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pricelist" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -435,6 +436,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>For painting , Add 10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Lock: $25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
